--- a/src/AssetValueAnalyzer.Web/wwwroot/samples/asset-values.xlsx
+++ b/src/AssetValueAnalyzer.Web/wwwroot/samples/asset-values.xlsx
@@ -2,79 +2,69 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Varlık Tablosu" sheetId="1" r:id="R883e818352754878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Varlık Tablosu" sheetId="1" r:id="R27e333c350914b0f"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">Tarih</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Varlık Tutarı</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="168" formatCode="&quot;₺&quot;#,##0.00"/>
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="mmm-yy"/>
+    <x:numFmt numFmtId="201" formatCode="&quot;₺&quot;#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FF15342F"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFEC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <x:xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <x:xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
-  <x:cellStyles count="4">
+  <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
-    <x:cellStyle name="Normal 2" xfId="1"/>
-    <x:cellStyle name="Normal 3 2" xfId="2"/>
-    <x:cellStyle name="Normal 4" xfId="3"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -82,34 +72,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -124,12 +114,12 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -155,7 +145,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -183,12 +173,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
         <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -196,6 +180,12 @@
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -211,7 +201,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -229,7 +219,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -264,190 +254,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+      <x:c r="A1" s="2" t="str">
+        <x:v>Tarih</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>Varlık Tutarı</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2">
+      <x:c r="A2" s="3" t="n">
         <x:v>44531</x:v>
       </x:c>
-      <x:c r="B2" s="3">
-        <x:v>1280000</x:v>
+      <x:c r="B2" s="4" t="n">
+        <x:v>1000000</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2">
+      <x:c r="A3" s="3" t="n">
         <x:v>44562</x:v>
       </x:c>
-      <x:c r="B3" s="3">
-        <x:v>1320000</x:v>
+      <x:c r="B3" s="4" t="n">
+        <x:v>1025000</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2">
+      <x:c r="A4" s="3" t="n">
         <x:v>44593</x:v>
       </x:c>
-      <x:c r="B4" s="3">
-        <x:v>1360000</x:v>
+      <x:c r="B4" s="4" t="n">
+        <x:v>1050000</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="2">
+      <x:c r="A5" s="3" t="n">
         <x:v>44621</x:v>
       </x:c>
-      <x:c r="B5" s="3">
+      <x:c r="B5" s="4" t="n">
+        <x:v>1075000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="3" t="n">
+        <x:v>44652</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="n">
+        <x:v>1100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="3" t="n">
+        <x:v>44682</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="n">
+        <x:v>1125000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="3" t="n">
+        <x:v>44713</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="n">
+        <x:v>1150000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="n">
+        <x:v>44743</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="n">
+        <x:v>1175000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="3" t="n">
+        <x:v>44774</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="n">
+        <x:v>44805</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="n">
+        <x:v>1225000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="n">
+        <x:v>44835</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="n">
+        <x:v>1250000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="n">
+        <x:v>44866</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="n">
+        <x:v>1275000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="n">
+        <x:v>44896</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="n">
+        <x:v>1300000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="n">
+        <x:v>44927</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="n">
+        <x:v>1325000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="n">
+        <x:v>44958</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="n">
+        <x:v>1350000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="n">
+        <x:v>44986</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="n">
+        <x:v>1375000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="n">
+        <x:v>45017</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="n">
         <x:v>1400000</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="2">
-        <x:v>44652</x:v>
-      </x:c>
-      <x:c r="B6" s="3">
-        <x:v>1440000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="2">
-        <x:v>44682</x:v>
-      </x:c>
-      <x:c r="B7" s="3">
-        <x:v>1480000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="2">
-        <x:v>44713</x:v>
-      </x:c>
-      <x:c r="B8" s="3">
-        <x:v>1520000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="2">
-        <x:v>44743</x:v>
-      </x:c>
-      <x:c r="B9" s="3">
-        <x:v>1560000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="2">
-        <x:v>44774</x:v>
-      </x:c>
-      <x:c r="B10" s="3">
-        <x:v>1600000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="2">
-        <x:v>44805</x:v>
-      </x:c>
-      <x:c r="B11" s="3">
-        <x:v>1640000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="2">
-        <x:v>44835</x:v>
-      </x:c>
-      <x:c r="B12" s="3">
-        <x:v>1680000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="2">
-        <x:v>44866</x:v>
-      </x:c>
-      <x:c r="B13" s="3">
-        <x:v>1720000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="2">
-        <x:v>44896</x:v>
-      </x:c>
-      <x:c r="B14" s="3">
-        <x:v>1760000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="2">
-        <x:v>44927</x:v>
-      </x:c>
-      <x:c r="B15" s="3">
-        <x:v>1800000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="2">
-        <x:v>44958</x:v>
-      </x:c>
-      <x:c r="B16" s="3">
-        <x:v>1840000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="2">
-        <x:v>44986</x:v>
-      </x:c>
-      <x:c r="B17" s="3">
-        <x:v>1880000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="2">
-        <x:v>45017</x:v>
-      </x:c>
-      <x:c r="B18" s="3">
-        <x:v>1920000</x:v>
-      </x:c>
-    </x:row>
     <x:row r="19">
-      <x:c r="A19" s="2">
+      <x:c r="A19" s="3" t="n">
         <x:v>45047</x:v>
       </x:c>
-      <x:c r="B19" s="3">
-        <x:v>1960000</x:v>
+      <x:c r="B19" s="4" t="n">
+        <x:v>1425000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="2">
+      <x:c r="A20" s="3" t="n">
         <x:v>45078</x:v>
       </x:c>
-      <x:c r="B20" s="3">
-        <x:v>2000000</x:v>
+      <x:c r="B20" s="4" t="n">
+        <x:v>1450000</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="2">
+      <x:c r="A21" s="3" t="n">
         <x:v>45108</x:v>
       </x:c>
-      <x:c r="B21" s="3">
-        <x:v>2040000</x:v>
+      <x:c r="B21" s="4" t="n">
+        <x:v>1475000</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="2">
+      <x:c r="A22" s="3" t="n">
         <x:v>45139</x:v>
       </x:c>
-      <x:c r="B22" s="3">
-        <x:v>2080000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
+      <x:c r="B22" s="4" t="n">
+        <x:v>1500000</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
